--- a/verification/report-samples/combined.xlsx
+++ b/verification/report-samples/combined.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Report" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$12</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -26,7 +26,7 @@
     <t>CYCLE INCOME DETAIL · TEST accounting period</t>
   </si>
   <si>
-    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-06T19:37:03.339+00:00</t>
+    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-11T16:34:22.859+00:00</t>
   </si>
   <si>
     <t>INCOMPLETE — missing mappings/sources; review notes.</t>
@@ -89,7 +89,7 @@
     <t>Diesel (Price)</t>
   </si>
   <si>
-    <t>Chln</t>
+    <t>Punjab Police</t>
   </si>
   <si>
     <t>Toll Plaza</t>
@@ -98,57 +98,57 @@
     <t>Food</t>
   </si>
   <si>
-    <t>inm</t>
-  </si>
-  <si>
-    <t>Other Exp.</t>
-  </si>
-  <si>
-    <t>Mobil Oil</t>
-  </si>
-  <si>
-    <t>Driver com</t>
-  </si>
-  <si>
-    <t>Total Exp.</t>
-  </si>
-  <si>
-    <t>Profit Loss</t>
-  </si>
-  <si>
-    <t>Travl (km)</t>
-  </si>
-  <si>
-    <t>Diesel (Ltr)</t>
-  </si>
-  <si>
-    <t>Avg Km/L</t>
+    <t>Inam / reward</t>
+  </si>
+  <si>
+    <t>Other expense</t>
+  </si>
+  <si>
+    <t>Engine oil</t>
+  </si>
+  <si>
+    <t>Driver cycle commission</t>
+  </si>
+  <si>
+    <t>Total expense</t>
+  </si>
+  <si>
+    <t>Profit / loss</t>
+  </si>
+  <si>
+    <t>Travel (km)</t>
+  </si>
+  <si>
+    <t>Diesel (L)</t>
+  </si>
+  <si>
+    <t>Average (km/L)</t>
+  </si>
+  <si>
+    <t>TEST gearbox structured invoice item</t>
+  </si>
+  <si>
+    <t>TEST Depot A / TEST Depot B</t>
+  </si>
+  <si>
+    <t>TEST cabin structured invoice item</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>TEST engine structured invoice item</t>
   </si>
   <si>
     <t>TEST body structured invoice item</t>
   </si>
   <si>
-    <t>TEST Depot A / TEST Depot B</t>
-  </si>
-  <si>
-    <t>TEST engine structured invoice item</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
     <t>TEST oil_change structured invoice item</t>
   </si>
   <si>
-    <t>TEST gearbox structured invoice item</t>
-  </si>
-  <si>
     <t>TEST tyres structured invoice item</t>
   </si>
   <si>
-    <t>TEST cabin structured invoice item</t>
-  </si>
-  <si>
     <t>VEHICLE SUMMARY</t>
   </si>
   <si>
@@ -164,9 +164,6 @@
     <t>Monthly Maintenance</t>
   </si>
   <si>
-    <t>Driver Commission</t>
-  </si>
-  <si>
     <t>TRACKER</t>
   </si>
   <si>
@@ -182,7 +179,7 @@
     <t>Driver settlement</t>
   </si>
   <si>
-    <t>Dr.Name</t>
+    <t>Driver name</t>
   </si>
   <si>
     <t>Driver Sale</t>
@@ -200,7 +197,7 @@
     <t>Salary Advance</t>
   </si>
   <si>
-    <t>Loan Install.</t>
+    <t>Loan installment</t>
   </si>
   <si>
     <t>Irresponsible Vehicle loss</t>
@@ -218,64 +215,60 @@
     <t>Total Loan</t>
   </si>
   <si>
-    <t>Loan Return</t>
-  </si>
-  <si>
-    <t>Loan left</t>
+    <t>Loan repaid</t>
+  </si>
+  <si>
+    <t>Loan balance</t>
+  </si>
+  <si>
+    <t>ENGINE</t>
+  </si>
+  <si>
+    <t>GEAR</t>
+  </si>
+  <si>
+    <t>BODY / CABIN</t>
+  </si>
+  <si>
+    <t>TYRES</t>
+  </si>
+  <si>
+    <t>TEST unposted engine work detail</t>
+  </si>
+  <si>
+    <t>TEST unposted gearbox work detail</t>
+  </si>
+  <si>
+    <t>TEST unposted tyres work detail</t>
+  </si>
+  <si>
+    <t>Total Bill</t>
+  </si>
+  <si>
+    <t>TEST unposted body work detail</t>
+  </si>
+  <si>
+    <t>TEST unposted cabin work detail</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>DRIVER SIGN</t>
-  </si>
-  <si>
-    <t>DRIVER THUMB</t>
-  </si>
-  <si>
-    <t>PAID BY</t>
-  </si>
-  <si>
-    <t>SIGN</t>
-  </si>
-  <si>
-    <t>PAID DATE</t>
-  </si>
-  <si>
-    <t>ENGINE</t>
-  </si>
-  <si>
-    <t>GEAR</t>
-  </si>
-  <si>
-    <t>BODY / CABIN</t>
-  </si>
-  <si>
-    <t>TYRES</t>
-  </si>
-  <si>
-    <t>TEST unposted engine work detail</t>
-  </si>
-  <si>
-    <t>TEST unposted gearbox work detail</t>
-  </si>
-  <si>
-    <t>TEST unposted tyres work detail</t>
-  </si>
-  <si>
-    <t>Total Bill</t>
-  </si>
-  <si>
-    <t>TEST unposted body work detail</t>
-  </si>
-  <si>
-    <t>TEST unposted cabin work detail</t>
-  </si>
-  <si>
-    <t>GBT SIGN</t>
-  </si>
-  <si>
-    <t>C.E.O. SIGN</t>
+    <t>Driver signature</t>
+  </si>
+  <si>
+    <t>Driver thumb impression</t>
+  </si>
+  <si>
+    <t>Paid by</t>
+  </si>
+  <si>
+    <t>Authorized signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature: __________________
+Name: ____________________
+Date: _____________________</t>
   </si>
   <si>
     <t>Vehicle Advance, Driver Sale, Mobile Load, deductions, tracker and printed settlement totals lack confirmed sources/calculations. Payment and signature spaces remain blank; this is not a finalized payment voucher.</t>
@@ -799,10 +792,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CF46"/>
+  <dimension ref="A1:CF42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="84" width="1.9" customWidth="1"/>
+    <col min="1" max="84" width="1.35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
@@ -1762,7 +1755,7 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="7">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -1773,7 +1766,7 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="6">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
@@ -1886,7 +1879,7 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="7">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -2001,12 +1994,12 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="7"/>
+      <c r="P15" s="7">
+        <v>500</v>
+      </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="7">
-        <v>200</v>
-      </c>
+      <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -2034,7 +2027,7 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="7">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -2068,12 +2061,12 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
+      <c r="S17" s="7">
+        <v>200</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
-      <c r="V17" s="7">
-        <v>300</v>
-      </c>
+      <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
     </row>
@@ -2097,15 +2090,15 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
-      <c r="P18" s="7">
-        <v>150</v>
-      </c>
+      <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
+      <c r="V18" s="7">
+        <v>300</v>
+      </c>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
@@ -2278,7 +2271,7 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
@@ -2290,7 +2283,7 @@
       <c r="AT22" s="3"/>
       <c r="AU22" s="3"/>
       <c r="AV22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AW22" s="3"/>
       <c r="AX22" s="3"/>
@@ -2301,7 +2294,7 @@
       <c r="BC22" s="3"/>
       <c r="BD22" s="3"/>
       <c r="BE22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="BF22" s="3"/>
       <c r="BG22" s="3"/>
@@ -2312,7 +2305,7 @@
       <c r="BL22" s="3"/>
       <c r="BM22" s="3"/>
       <c r="BN22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3"/>
@@ -2324,7 +2317,7 @@
       <c r="BV22" s="3"/>
       <c r="BW22" s="3"/>
       <c r="BX22" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="BY22" s="3"/>
       <c r="BZ22" s="3"/>
@@ -2433,7 +2426,7 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2521,14 +2514,14 @@
     </row>
     <row r="26" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -2536,14 +2529,14 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -2557,7 +2550,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
@@ -2565,28 +2558,28 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
       <c r="AG26" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AH26" s="3"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM26" s="3"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="3"/>
       <c r="AQ26" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AR26" s="3"/>
       <c r="AS26" s="3"/>
       <c r="AT26" s="3"/>
       <c r="AU26" s="3"/>
       <c r="AV26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AW26" s="3"/>
       <c r="AX26" s="3"/>
@@ -2594,28 +2587,28 @@
       <c r="AZ26" s="3"/>
       <c r="BA26" s="3"/>
       <c r="BB26" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BC26" s="3"/>
       <c r="BD26" s="3"/>
       <c r="BE26" s="3"/>
       <c r="BF26" s="3"/>
       <c r="BG26" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BH26" s="3"/>
       <c r="BI26" s="3"/>
       <c r="BJ26" s="3"/>
       <c r="BK26" s="3"/>
       <c r="BL26" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BM26" s="3"/>
       <c r="BN26" s="3"/>
       <c r="BO26" s="3"/>
       <c r="BP26" s="3"/>
       <c r="BQ26" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="BR26" s="3"/>
       <c r="BS26" s="3"/>
@@ -2623,14 +2616,14 @@
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
       <c r="BW26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="BX26" s="3"/>
       <c r="BY26" s="3"/>
       <c r="BZ26" s="3"/>
       <c r="CA26" s="3"/>
       <c r="CB26" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="CC26" s="3"/>
       <c r="CD26" s="3"/>
@@ -2735,7 +2728,7 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2757,7 +2750,9 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
+      <c r="V29" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
@@ -2778,7 +2773,9 @@
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="3"/>
-      <c r="AQ29" s="3"/>
+      <c r="AQ29" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="AR29" s="3"/>
       <c r="AS29" s="3"/>
       <c r="AT29" s="3"/>
@@ -2799,7 +2796,9 @@
       <c r="BI29" s="3"/>
       <c r="BJ29" s="3"/>
       <c r="BK29" s="3"/>
-      <c r="BL29" s="3"/>
+      <c r="BL29" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="BM29" s="3"/>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
@@ -2823,14 +2822,16 @@
     </row>
     <row r="30" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -2840,47 +2841,53 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="Q30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
+      <c r="V30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
-      <c r="AB30" s="3"/>
+      <c r="AB30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
-      <c r="AI30" s="3" t="s">
-        <v>72</v>
-      </c>
+      <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
-      <c r="AL30" s="3"/>
+      <c r="AL30" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="3"/>
-      <c r="AQ30" s="3"/>
+      <c r="AQ30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AR30" s="3"/>
       <c r="AS30" s="3"/>
       <c r="AT30" s="3"/>
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
-      <c r="AW30" s="3"/>
+      <c r="AW30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AX30" s="3"/>
-      <c r="AY30" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="AY30" s="3"/>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3"/>
@@ -2888,20 +2895,24 @@
       <c r="BD30" s="3"/>
       <c r="BE30" s="3"/>
       <c r="BF30" s="3"/>
-      <c r="BG30" s="3"/>
+      <c r="BG30" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3"/>
       <c r="BJ30" s="3"/>
       <c r="BK30" s="3"/>
-      <c r="BL30" s="3"/>
+      <c r="BL30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="BM30" s="3"/>
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
-      <c r="BP30" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="BP30" s="3"/>
       <c r="BQ30" s="3"/>
-      <c r="BR30" s="3"/>
+      <c r="BR30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="BS30" s="3"/>
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
@@ -2911,20 +2922,26 @@
       <c r="BY30" s="3"/>
       <c r="BZ30" s="3"/>
       <c r="CA30" s="3"/>
-      <c r="CB30" s="3"/>
+      <c r="CB30" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="CC30" s="3"/>
       <c r="CD30" s="3"/>
       <c r="CE30" s="3"/>
       <c r="CF30" s="3"/>
     </row>
-    <row r="31" ht="42" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+    <row r="31" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
@@ -2934,18 +2951,24 @@
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5"/>
-      <c r="Z31" s="5"/>
-      <c r="AA31" s="5"/>
-      <c r="AB31" s="5"/>
+      <c r="Q31" s="7">
+        <v>500</v>
+      </c>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="6">
+        <v>46023</v>
+      </c>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
@@ -2955,18 +2978,24 @@
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
       <c r="AK31" s="5"/>
-      <c r="AL31" s="5"/>
-      <c r="AM31" s="5"/>
-      <c r="AN31" s="5"/>
-      <c r="AO31" s="5"/>
-      <c r="AP31" s="5"/>
-      <c r="AQ31" s="5"/>
-      <c r="AR31" s="5"/>
-      <c r="AS31" s="5"/>
-      <c r="AT31" s="5"/>
-      <c r="AU31" s="5"/>
-      <c r="AV31" s="5"/>
-      <c r="AW31" s="5"/>
+      <c r="AL31" s="7">
+        <v>250</v>
+      </c>
+      <c r="AM31" s="7"/>
+      <c r="AN31" s="7"/>
+      <c r="AO31" s="7"/>
+      <c r="AP31" s="7"/>
+      <c r="AQ31" s="6">
+        <v>46023</v>
+      </c>
+      <c r="AR31" s="6"/>
+      <c r="AS31" s="6"/>
+      <c r="AT31" s="6"/>
+      <c r="AU31" s="6"/>
+      <c r="AV31" s="6"/>
+      <c r="AW31" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="AX31" s="5"/>
       <c r="AY31" s="5"/>
       <c r="AZ31" s="5"/>
@@ -2976,1039 +3005,745 @@
       <c r="BD31" s="5"/>
       <c r="BE31" s="5"/>
       <c r="BF31" s="5"/>
-      <c r="BG31" s="5"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="5"/>
-      <c r="BJ31" s="5"/>
-      <c r="BK31" s="5"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="5"/>
-      <c r="BN31" s="5"/>
-      <c r="BO31" s="5"/>
+      <c r="BG31" s="7">
+        <v>150</v>
+      </c>
+      <c r="BH31" s="7"/>
+      <c r="BI31" s="7"/>
+      <c r="BJ31" s="7"/>
+      <c r="BK31" s="7"/>
+      <c r="BL31" s="6">
+        <v>46023</v>
+      </c>
+      <c r="BM31" s="6"/>
+      <c r="BN31" s="6"/>
+      <c r="BO31" s="6"/>
       <c r="BP31" s="6"/>
       <c r="BQ31" s="6"/>
-      <c r="BR31" s="6"/>
-      <c r="BS31" s="6"/>
-      <c r="BT31" s="6"/>
-      <c r="BU31" s="6"/>
-      <c r="BV31" s="6"/>
-      <c r="BW31" s="6"/>
-      <c r="BX31" s="6"/>
-      <c r="BY31" s="6"/>
-      <c r="BZ31" s="6"/>
-      <c r="CA31" s="6"/>
-      <c r="CB31" s="6"/>
-      <c r="CC31" s="6"/>
-      <c r="CD31" s="6"/>
-      <c r="CE31" s="6"/>
-      <c r="CF31" s="6"/>
+      <c r="BR31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="BS31" s="5"/>
+      <c r="BT31" s="5"/>
+      <c r="BU31" s="5"/>
+      <c r="BV31" s="5"/>
+      <c r="BW31" s="5"/>
+      <c r="BX31" s="5"/>
+      <c r="BY31" s="5"/>
+      <c r="BZ31" s="5"/>
+      <c r="CA31" s="5"/>
+      <c r="CB31" s="7">
+        <v>300</v>
+      </c>
+      <c r="CC31" s="7"/>
+      <c r="CD31" s="7"/>
+      <c r="CE31" s="7"/>
+      <c r="CF31" s="7"/>
     </row>
-    <row r="33" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+    <row r="32" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC32" s="5"/>
+      <c r="AD32" s="5"/>
+      <c r="AE32" s="5"/>
+      <c r="AF32" s="5"/>
+      <c r="AG32" s="5"/>
+      <c r="AH32" s="5"/>
+      <c r="AI32" s="5"/>
+      <c r="AJ32" s="5"/>
+      <c r="AK32" s="5"/>
+      <c r="AL32" s="7"/>
+      <c r="AM32" s="7"/>
+      <c r="AN32" s="7"/>
+      <c r="AO32" s="7"/>
+      <c r="AP32" s="7"/>
+      <c r="AQ32" s="6">
+        <v>46023</v>
+      </c>
+      <c r="AR32" s="6"/>
+      <c r="AS32" s="6"/>
+      <c r="AT32" s="6"/>
+      <c r="AU32" s="6"/>
+      <c r="AV32" s="6"/>
+      <c r="AW32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AX32" s="5"/>
+      <c r="AY32" s="5"/>
+      <c r="AZ32" s="5"/>
+      <c r="BA32" s="5"/>
+      <c r="BB32" s="5"/>
+      <c r="BC32" s="5"/>
+      <c r="BD32" s="5"/>
+      <c r="BE32" s="5"/>
+      <c r="BF32" s="5"/>
+      <c r="BG32" s="7">
+        <v>400</v>
+      </c>
+      <c r="BH32" s="7"/>
+      <c r="BI32" s="7"/>
+      <c r="BJ32" s="7"/>
+      <c r="BK32" s="7"/>
+      <c r="BL32" s="6"/>
+      <c r="BM32" s="6"/>
+      <c r="BN32" s="6"/>
+      <c r="BO32" s="6"/>
+      <c r="BP32" s="6"/>
+      <c r="BQ32" s="6"/>
+      <c r="BR32" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS32" s="5"/>
+      <c r="BT32" s="5"/>
+      <c r="BU32" s="5"/>
+      <c r="BV32" s="5"/>
+      <c r="BW32" s="5"/>
+      <c r="BX32" s="5"/>
+      <c r="BY32" s="5"/>
+      <c r="BZ32" s="5"/>
+      <c r="CA32" s="5"/>
+      <c r="CB32" s="7"/>
+      <c r="CC32" s="7"/>
+      <c r="CD32" s="7"/>
+      <c r="CE32" s="7"/>
+      <c r="CF32" s="7"/>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3" t="s">
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="12">
+        <v>500</v>
+      </c>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC33" s="11"/>
+      <c r="AD33" s="11"/>
+      <c r="AE33" s="11"/>
+      <c r="AF33" s="11"/>
+      <c r="AG33" s="11"/>
+      <c r="AH33" s="11"/>
+      <c r="AI33" s="11"/>
+      <c r="AJ33" s="11"/>
+      <c r="AK33" s="11"/>
+      <c r="AL33" s="12">
+        <v>250</v>
+      </c>
+      <c r="AM33" s="12"/>
+      <c r="AN33" s="12"/>
+      <c r="AO33" s="12"/>
+      <c r="AP33" s="12"/>
+      <c r="AQ33" s="6"/>
+      <c r="AR33" s="6"/>
+      <c r="AS33" s="6"/>
+      <c r="AT33" s="6"/>
+      <c r="AU33" s="6"/>
+      <c r="AV33" s="6"/>
+      <c r="AW33" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="3"/>
-      <c r="AC33" s="3"/>
-      <c r="AD33" s="3"/>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="3"/>
-      <c r="AG33" s="3"/>
-      <c r="AH33" s="3"/>
-      <c r="AI33" s="3"/>
-      <c r="AJ33" s="3"/>
-      <c r="AK33" s="3"/>
-      <c r="AL33" s="3"/>
-      <c r="AM33" s="3"/>
-      <c r="AN33" s="3"/>
-      <c r="AO33" s="3"/>
-      <c r="AP33" s="3"/>
-      <c r="AQ33" s="3" t="s">
+      <c r="AX33" s="5"/>
+      <c r="AY33" s="5"/>
+      <c r="AZ33" s="5"/>
+      <c r="BA33" s="5"/>
+      <c r="BB33" s="5"/>
+      <c r="BC33" s="5"/>
+      <c r="BD33" s="5"/>
+      <c r="BE33" s="5"/>
+      <c r="BF33" s="5"/>
+      <c r="BG33" s="7"/>
+      <c r="BH33" s="7"/>
+      <c r="BI33" s="7"/>
+      <c r="BJ33" s="7"/>
+      <c r="BK33" s="7"/>
+      <c r="BL33" s="10"/>
+      <c r="BM33" s="10"/>
+      <c r="BN33" s="10"/>
+      <c r="BO33" s="10"/>
+      <c r="BP33" s="10"/>
+      <c r="BQ33" s="10"/>
+      <c r="BR33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="BS33" s="11"/>
+      <c r="BT33" s="11"/>
+      <c r="BU33" s="11"/>
+      <c r="BV33" s="11"/>
+      <c r="BW33" s="11"/>
+      <c r="BX33" s="11"/>
+      <c r="BY33" s="11"/>
+      <c r="BZ33" s="11"/>
+      <c r="CA33" s="11"/>
+      <c r="CB33" s="12">
+        <v>300</v>
+      </c>
+      <c r="CC33" s="12"/>
+      <c r="CD33" s="12"/>
+      <c r="CE33" s="12"/>
+      <c r="CF33" s="12"/>
+    </row>
+    <row r="34" ht="26" customHeight="1" spans="43:63" x14ac:dyDescent="0.25">
+      <c r="AQ34" s="6"/>
+      <c r="AR34" s="6"/>
+      <c r="AS34" s="6"/>
+      <c r="AT34" s="6"/>
+      <c r="AU34" s="6"/>
+      <c r="AV34" s="6"/>
+      <c r="AW34" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="AR33" s="3"/>
-      <c r="AS33" s="3"/>
-      <c r="AT33" s="3"/>
-      <c r="AU33" s="3"/>
-      <c r="AV33" s="3"/>
-      <c r="AW33" s="3"/>
-      <c r="AX33" s="3"/>
-      <c r="AY33" s="3"/>
-      <c r="AZ33" s="3"/>
-      <c r="BA33" s="3"/>
-      <c r="BB33" s="3"/>
-      <c r="BC33" s="3"/>
-      <c r="BD33" s="3"/>
-      <c r="BE33" s="3"/>
-      <c r="BF33" s="3"/>
-      <c r="BG33" s="3"/>
-      <c r="BH33" s="3"/>
-      <c r="BI33" s="3"/>
-      <c r="BJ33" s="3"/>
-      <c r="BK33" s="3"/>
-      <c r="BL33" s="3" t="s">
+      <c r="AX34" s="5"/>
+      <c r="AY34" s="5"/>
+      <c r="AZ34" s="5"/>
+      <c r="BA34" s="5"/>
+      <c r="BB34" s="5"/>
+      <c r="BC34" s="5"/>
+      <c r="BD34" s="5"/>
+      <c r="BE34" s="5"/>
+      <c r="BF34" s="5"/>
+      <c r="BG34" s="7"/>
+      <c r="BH34" s="7"/>
+      <c r="BI34" s="7"/>
+      <c r="BJ34" s="7"/>
+      <c r="BK34" s="7"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="43:63" x14ac:dyDescent="0.25">
+      <c r="AQ35" s="10"/>
+      <c r="AR35" s="10"/>
+      <c r="AS35" s="10"/>
+      <c r="AT35" s="10"/>
+      <c r="AU35" s="10"/>
+      <c r="AV35" s="10"/>
+      <c r="AW35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX35" s="11"/>
+      <c r="AY35" s="11"/>
+      <c r="AZ35" s="11"/>
+      <c r="BA35" s="11"/>
+      <c r="BB35" s="11"/>
+      <c r="BC35" s="11"/>
+      <c r="BD35" s="11"/>
+      <c r="BE35" s="11"/>
+      <c r="BF35" s="11"/>
+      <c r="BG35" s="12">
+        <v>550</v>
+      </c>
+      <c r="BH35" s="12"/>
+      <c r="BI35" s="12"/>
+      <c r="BJ35" s="12"/>
+      <c r="BK35" s="12"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="BM33" s="3"/>
-      <c r="BN33" s="3"/>
-      <c r="BO33" s="3"/>
-      <c r="BP33" s="3"/>
-      <c r="BQ33" s="3"/>
-      <c r="BR33" s="3"/>
-      <c r="BS33" s="3"/>
-      <c r="BT33" s="3"/>
-      <c r="BU33" s="3"/>
-      <c r="BV33" s="3"/>
-      <c r="BW33" s="3"/>
-      <c r="BX33" s="3"/>
-      <c r="BY33" s="3"/>
-      <c r="BZ33" s="3"/>
-      <c r="CA33" s="3"/>
-      <c r="CB33" s="3"/>
-      <c r="CC33" s="3"/>
-      <c r="CD33" s="3"/>
-      <c r="CE33" s="3"/>
-      <c r="CF33" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="3"/>
+      <c r="AI37" s="3"/>
+      <c r="AJ37" s="3"/>
+      <c r="AK37" s="3"/>
+      <c r="AL37" s="3"/>
+      <c r="AM37" s="3"/>
+      <c r="AN37" s="3"/>
+      <c r="AO37" s="3"/>
+      <c r="AP37" s="3"/>
+      <c r="AQ37" s="3"/>
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="3"/>
+      <c r="AT37" s="3"/>
+      <c r="AU37" s="3"/>
+      <c r="AV37" s="3"/>
+      <c r="AW37" s="3"/>
+      <c r="AX37" s="3"/>
+      <c r="AY37" s="3"/>
+      <c r="AZ37" s="3"/>
+      <c r="BA37" s="3"/>
+      <c r="BB37" s="3"/>
+      <c r="BC37" s="3"/>
+      <c r="BD37" s="3"/>
+      <c r="BE37" s="3"/>
+      <c r="BF37" s="3"/>
+      <c r="BG37" s="3"/>
+      <c r="BH37" s="3"/>
+      <c r="BI37" s="3"/>
+      <c r="BJ37" s="3"/>
+      <c r="BK37" s="3"/>
+      <c r="BL37" s="3"/>
+      <c r="BM37" s="3"/>
+      <c r="BN37" s="3"/>
+      <c r="BO37" s="3"/>
+      <c r="BP37" s="3"/>
+      <c r="BQ37" s="3"/>
+      <c r="BR37" s="3"/>
+      <c r="BS37" s="3"/>
+      <c r="BT37" s="3"/>
+      <c r="BU37" s="3"/>
+      <c r="BV37" s="3"/>
+      <c r="BW37" s="3"/>
+      <c r="BX37" s="3"/>
+      <c r="BY37" s="3"/>
+      <c r="BZ37" s="3"/>
+      <c r="CA37" s="3"/>
+      <c r="CB37" s="3"/>
+      <c r="CC37" s="3"/>
+      <c r="CD37" s="3"/>
+      <c r="CE37" s="3"/>
+      <c r="CF37" s="3"/>
     </row>
-    <row r="34" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB34" s="3"/>
-      <c r="AC34" s="3"/>
-      <c r="AD34" s="3"/>
-      <c r="AE34" s="3"/>
-      <c r="AF34" s="3"/>
-      <c r="AG34" s="3"/>
-      <c r="AH34" s="3"/>
-      <c r="AI34" s="3"/>
-      <c r="AJ34" s="3"/>
-      <c r="AK34" s="3"/>
-      <c r="AL34" s="3"/>
-      <c r="AM34" s="3"/>
-      <c r="AN34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO34" s="3"/>
-      <c r="AP34" s="3"/>
-      <c r="AQ34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AR34" s="3"/>
-      <c r="AS34" s="3"/>
-      <c r="AT34" s="3"/>
-      <c r="AU34" s="3"/>
-      <c r="AV34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AW34" s="3"/>
-      <c r="AX34" s="3"/>
-      <c r="AY34" s="3"/>
-      <c r="AZ34" s="3"/>
-      <c r="BA34" s="3"/>
-      <c r="BB34" s="3"/>
-      <c r="BC34" s="3"/>
-      <c r="BD34" s="3"/>
-      <c r="BE34" s="3"/>
-      <c r="BF34" s="3"/>
-      <c r="BG34" s="3"/>
-      <c r="BH34" s="3"/>
-      <c r="BI34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="BJ34" s="3"/>
-      <c r="BK34" s="3"/>
-      <c r="BL34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="BM34" s="3"/>
-      <c r="BN34" s="3"/>
-      <c r="BO34" s="3"/>
-      <c r="BP34" s="3"/>
-      <c r="BQ34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="BR34" s="3"/>
-      <c r="BS34" s="3"/>
-      <c r="BT34" s="3"/>
-      <c r="BU34" s="3"/>
-      <c r="BV34" s="3"/>
-      <c r="BW34" s="3"/>
-      <c r="BX34" s="3"/>
-      <c r="BY34" s="3"/>
-      <c r="BZ34" s="3"/>
-      <c r="CA34" s="3"/>
-      <c r="CB34" s="3"/>
-      <c r="CC34" s="3"/>
-      <c r="CD34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="CE34" s="3"/>
-      <c r="CF34" s="3"/>
+    <row r="38" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="3"/>
+      <c r="AJ38" s="3"/>
+      <c r="AK38" s="3"/>
+      <c r="AL38" s="3"/>
+      <c r="AM38" s="3"/>
+      <c r="AN38" s="3"/>
+      <c r="AO38" s="3"/>
+      <c r="AP38" s="3"/>
+      <c r="AQ38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR38" s="3"/>
+      <c r="AS38" s="3"/>
+      <c r="AT38" s="3"/>
+      <c r="AU38" s="3"/>
+      <c r="AV38" s="3"/>
+      <c r="AW38" s="3"/>
+      <c r="AX38" s="3"/>
+      <c r="AY38" s="3"/>
+      <c r="AZ38" s="3"/>
+      <c r="BA38" s="3"/>
+      <c r="BB38" s="3"/>
+      <c r="BC38" s="3"/>
+      <c r="BD38" s="3"/>
+      <c r="BE38" s="3"/>
+      <c r="BF38" s="3"/>
+      <c r="BG38" s="3"/>
+      <c r="BH38" s="3"/>
+      <c r="BI38" s="3"/>
+      <c r="BJ38" s="3"/>
+      <c r="BK38" s="3"/>
+      <c r="BL38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM38" s="3"/>
+      <c r="BN38" s="3"/>
+      <c r="BO38" s="3"/>
+      <c r="BP38" s="3"/>
+      <c r="BQ38" s="3"/>
+      <c r="BR38" s="3"/>
+      <c r="BS38" s="3"/>
+      <c r="BT38" s="3"/>
+      <c r="BU38" s="3"/>
+      <c r="BV38" s="3"/>
+      <c r="BW38" s="3"/>
+      <c r="BX38" s="3"/>
+      <c r="BY38" s="3"/>
+      <c r="BZ38" s="3"/>
+      <c r="CA38" s="3"/>
+      <c r="CB38" s="3"/>
+      <c r="CC38" s="3"/>
+      <c r="CD38" s="3"/>
+      <c r="CE38" s="3"/>
+      <c r="CF38" s="3"/>
     </row>
-    <row r="35" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>46023</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="7">
-        <v>500</v>
-      </c>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="6">
-        <v>46023</v>
-      </c>
-      <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB35" s="5"/>
-      <c r="AC35" s="5"/>
-      <c r="AD35" s="5"/>
-      <c r="AE35" s="5"/>
-      <c r="AF35" s="5"/>
-      <c r="AG35" s="5"/>
-      <c r="AH35" s="5"/>
-      <c r="AI35" s="5"/>
-      <c r="AJ35" s="5"/>
-      <c r="AK35" s="5"/>
-      <c r="AL35" s="5"/>
-      <c r="AM35" s="5"/>
-      <c r="AN35" s="7">
-        <v>250</v>
-      </c>
-      <c r="AO35" s="7"/>
-      <c r="AP35" s="7"/>
-      <c r="AQ35" s="6">
-        <v>46023</v>
-      </c>
-      <c r="AR35" s="6"/>
-      <c r="AS35" s="6"/>
-      <c r="AT35" s="6"/>
-      <c r="AU35" s="6"/>
-      <c r="AV35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW35" s="5"/>
-      <c r="AX35" s="5"/>
-      <c r="AY35" s="5"/>
-      <c r="AZ35" s="5"/>
-      <c r="BA35" s="5"/>
-      <c r="BB35" s="5"/>
-      <c r="BC35" s="5"/>
-      <c r="BD35" s="5"/>
-      <c r="BE35" s="5"/>
-      <c r="BF35" s="5"/>
-      <c r="BG35" s="5"/>
-      <c r="BH35" s="5"/>
-      <c r="BI35" s="7">
-        <v>400</v>
-      </c>
-      <c r="BJ35" s="7"/>
-      <c r="BK35" s="7"/>
-      <c r="BL35" s="6">
-        <v>46023</v>
-      </c>
-      <c r="BM35" s="6"/>
-      <c r="BN35" s="6"/>
-      <c r="BO35" s="6"/>
-      <c r="BP35" s="6"/>
-      <c r="BQ35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="BR35" s="5"/>
-      <c r="BS35" s="5"/>
-      <c r="BT35" s="5"/>
-      <c r="BU35" s="5"/>
-      <c r="BV35" s="5"/>
-      <c r="BW35" s="5"/>
-      <c r="BX35" s="5"/>
-      <c r="BY35" s="5"/>
-      <c r="BZ35" s="5"/>
-      <c r="CA35" s="5"/>
-      <c r="CB35" s="5"/>
-      <c r="CC35" s="5"/>
-      <c r="CD35" s="7">
-        <v>300</v>
-      </c>
-      <c r="CE35" s="7"/>
-      <c r="CF35" s="7"/>
+    <row r="39" ht="85" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="5"/>
+      <c r="AB39" s="5"/>
+      <c r="AC39" s="5"/>
+      <c r="AD39" s="5"/>
+      <c r="AE39" s="5"/>
+      <c r="AF39" s="5"/>
+      <c r="AG39" s="5"/>
+      <c r="AH39" s="5"/>
+      <c r="AI39" s="5"/>
+      <c r="AJ39" s="5"/>
+      <c r="AK39" s="5"/>
+      <c r="AL39" s="5"/>
+      <c r="AM39" s="5"/>
+      <c r="AN39" s="5"/>
+      <c r="AO39" s="5"/>
+      <c r="AP39" s="5"/>
+      <c r="AQ39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR39" s="5"/>
+      <c r="AS39" s="5"/>
+      <c r="AT39" s="5"/>
+      <c r="AU39" s="5"/>
+      <c r="AV39" s="5"/>
+      <c r="AW39" s="5"/>
+      <c r="AX39" s="5"/>
+      <c r="AY39" s="5"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="5"/>
+      <c r="BB39" s="5"/>
+      <c r="BC39" s="5"/>
+      <c r="BD39" s="5"/>
+      <c r="BE39" s="5"/>
+      <c r="BF39" s="5"/>
+      <c r="BG39" s="5"/>
+      <c r="BH39" s="5"/>
+      <c r="BI39" s="5"/>
+      <c r="BJ39" s="5"/>
+      <c r="BK39" s="5"/>
+      <c r="BL39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM39" s="5"/>
+      <c r="BN39" s="5"/>
+      <c r="BO39" s="5"/>
+      <c r="BP39" s="5"/>
+      <c r="BQ39" s="5"/>
+      <c r="BR39" s="5"/>
+      <c r="BS39" s="5"/>
+      <c r="BT39" s="5"/>
+      <c r="BU39" s="5"/>
+      <c r="BV39" s="5"/>
+      <c r="BW39" s="5"/>
+      <c r="BX39" s="5"/>
+      <c r="BY39" s="5"/>
+      <c r="BZ39" s="5"/>
+      <c r="CA39" s="5"/>
+      <c r="CB39" s="5"/>
+      <c r="CC39" s="5"/>
+      <c r="CD39" s="5"/>
+      <c r="CE39" s="5"/>
+      <c r="CF39" s="5"/>
     </row>
-    <row r="36" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB36" s="5"/>
-      <c r="AC36" s="5"/>
-      <c r="AD36" s="5"/>
-      <c r="AE36" s="5"/>
-      <c r="AF36" s="5"/>
-      <c r="AG36" s="5"/>
-      <c r="AH36" s="5"/>
-      <c r="AI36" s="5"/>
-      <c r="AJ36" s="5"/>
-      <c r="AK36" s="5"/>
-      <c r="AL36" s="5"/>
-      <c r="AM36" s="5"/>
-      <c r="AN36" s="7"/>
-      <c r="AO36" s="7"/>
-      <c r="AP36" s="7"/>
-      <c r="AQ36" s="6">
-        <v>46023</v>
-      </c>
-      <c r="AR36" s="6"/>
-      <c r="AS36" s="6"/>
-      <c r="AT36" s="6"/>
-      <c r="AU36" s="6"/>
-      <c r="AV36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AW36" s="5"/>
-      <c r="AX36" s="5"/>
-      <c r="AY36" s="5"/>
-      <c r="AZ36" s="5"/>
-      <c r="BA36" s="5"/>
-      <c r="BB36" s="5"/>
-      <c r="BC36" s="5"/>
-      <c r="BD36" s="5"/>
-      <c r="BE36" s="5"/>
-      <c r="BF36" s="5"/>
-      <c r="BG36" s="5"/>
-      <c r="BH36" s="5"/>
-      <c r="BI36" s="7">
-        <v>150</v>
-      </c>
-      <c r="BJ36" s="7"/>
-      <c r="BK36" s="7"/>
-      <c r="BL36" s="6"/>
-      <c r="BM36" s="6"/>
-      <c r="BN36" s="6"/>
-      <c r="BO36" s="6"/>
-      <c r="BP36" s="6"/>
-      <c r="BQ36" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="BR36" s="5"/>
-      <c r="BS36" s="5"/>
-      <c r="BT36" s="5"/>
-      <c r="BU36" s="5"/>
-      <c r="BV36" s="5"/>
-      <c r="BW36" s="5"/>
-      <c r="BX36" s="5"/>
-      <c r="BY36" s="5"/>
-      <c r="BZ36" s="5"/>
-      <c r="CA36" s="5"/>
-      <c r="CB36" s="5"/>
-      <c r="CC36" s="5"/>
-      <c r="CD36" s="7"/>
-      <c r="CE36" s="7"/>
-      <c r="CF36" s="7"/>
+    <row r="41" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="2"/>
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="2"/>
+      <c r="AE41" s="2"/>
+      <c r="AF41" s="2"/>
+      <c r="AG41" s="2"/>
+      <c r="AH41" s="2"/>
+      <c r="AI41" s="2"/>
+      <c r="AJ41" s="2"/>
+      <c r="AK41" s="2"/>
+      <c r="AL41" s="2"/>
+      <c r="AM41" s="2"/>
+      <c r="AN41" s="2"/>
+      <c r="AO41" s="2"/>
+      <c r="AP41" s="2"/>
+      <c r="AQ41" s="2"/>
+      <c r="AR41" s="2"/>
+      <c r="AS41" s="2"/>
+      <c r="AT41" s="2"/>
+      <c r="AU41" s="2"/>
+      <c r="AV41" s="2"/>
+      <c r="AW41" s="2"/>
+      <c r="AX41" s="2"/>
+      <c r="AY41" s="2"/>
+      <c r="AZ41" s="2"/>
+      <c r="BA41" s="2"/>
+      <c r="BB41" s="2"/>
+      <c r="BC41" s="2"/>
+      <c r="BD41" s="2"/>
+      <c r="BE41" s="2"/>
+      <c r="BF41" s="2"/>
+      <c r="BG41" s="2"/>
+      <c r="BH41" s="2"/>
+      <c r="BI41" s="2"/>
+      <c r="BJ41" s="2"/>
+      <c r="BK41" s="2"/>
+      <c r="BL41" s="2"/>
+      <c r="BM41" s="2"/>
+      <c r="BN41" s="2"/>
+      <c r="BO41" s="2"/>
+      <c r="BP41" s="2"/>
+      <c r="BQ41" s="2"/>
+      <c r="BR41" s="2"/>
+      <c r="BS41" s="2"/>
+      <c r="BT41" s="2"/>
+      <c r="BU41" s="2"/>
+      <c r="BV41" s="2"/>
+      <c r="BW41" s="2"/>
+      <c r="BX41" s="2"/>
+      <c r="BY41" s="2"/>
+      <c r="BZ41" s="2"/>
+      <c r="CA41" s="2"/>
+      <c r="CB41" s="2"/>
+      <c r="CC41" s="2"/>
+      <c r="CD41" s="2"/>
+      <c r="CE41" s="2"/>
+      <c r="CF41" s="2"/>
     </row>
-    <row r="37" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="12">
-        <v>500</v>
-      </c>
-      <c r="T37" s="12"/>
-      <c r="U37" s="12"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10"/>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="10"/>
-      <c r="AA37" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB37" s="11"/>
-      <c r="AC37" s="11"/>
-      <c r="AD37" s="11"/>
-      <c r="AE37" s="11"/>
-      <c r="AF37" s="11"/>
-      <c r="AG37" s="11"/>
-      <c r="AH37" s="11"/>
-      <c r="AI37" s="11"/>
-      <c r="AJ37" s="11"/>
-      <c r="AK37" s="11"/>
-      <c r="AL37" s="11"/>
-      <c r="AM37" s="11"/>
-      <c r="AN37" s="12">
-        <v>250</v>
-      </c>
-      <c r="AO37" s="12"/>
-      <c r="AP37" s="12"/>
-      <c r="AQ37" s="6"/>
-      <c r="AR37" s="6"/>
-      <c r="AS37" s="6"/>
-      <c r="AT37" s="6"/>
-      <c r="AU37" s="6"/>
-      <c r="AV37" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW37" s="5"/>
-      <c r="AX37" s="5"/>
-      <c r="AY37" s="5"/>
-      <c r="AZ37" s="5"/>
-      <c r="BA37" s="5"/>
-      <c r="BB37" s="5"/>
-      <c r="BC37" s="5"/>
-      <c r="BD37" s="5"/>
-      <c r="BE37" s="5"/>
-      <c r="BF37" s="5"/>
-      <c r="BG37" s="5"/>
-      <c r="BH37" s="5"/>
-      <c r="BI37" s="7"/>
-      <c r="BJ37" s="7"/>
-      <c r="BK37" s="7"/>
-      <c r="BL37" s="10"/>
-      <c r="BM37" s="10"/>
-      <c r="BN37" s="10"/>
-      <c r="BO37" s="10"/>
-      <c r="BP37" s="10"/>
-      <c r="BQ37" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="BR37" s="11"/>
-      <c r="BS37" s="11"/>
-      <c r="BT37" s="11"/>
-      <c r="BU37" s="11"/>
-      <c r="BV37" s="11"/>
-      <c r="BW37" s="11"/>
-      <c r="BX37" s="11"/>
-      <c r="BY37" s="11"/>
-      <c r="BZ37" s="11"/>
-      <c r="CA37" s="11"/>
-      <c r="CB37" s="11"/>
-      <c r="CC37" s="11"/>
-      <c r="CD37" s="12">
-        <v>300</v>
-      </c>
-      <c r="CE37" s="12"/>
-      <c r="CF37" s="12"/>
-    </row>
-    <row r="38" ht="26" customHeight="1" spans="43:63" x14ac:dyDescent="0.25">
-      <c r="AQ38" s="6"/>
-      <c r="AR38" s="6"/>
-      <c r="AS38" s="6"/>
-      <c r="AT38" s="6"/>
-      <c r="AU38" s="6"/>
-      <c r="AV38" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW38" s="5"/>
-      <c r="AX38" s="5"/>
-      <c r="AY38" s="5"/>
-      <c r="AZ38" s="5"/>
-      <c r="BA38" s="5"/>
-      <c r="BB38" s="5"/>
-      <c r="BC38" s="5"/>
-      <c r="BD38" s="5"/>
-      <c r="BE38" s="5"/>
-      <c r="BF38" s="5"/>
-      <c r="BG38" s="5"/>
-      <c r="BH38" s="5"/>
-      <c r="BI38" s="7"/>
-      <c r="BJ38" s="7"/>
-      <c r="BK38" s="7"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="43:63" x14ac:dyDescent="0.25">
-      <c r="AQ39" s="10"/>
-      <c r="AR39" s="10"/>
-      <c r="AS39" s="10"/>
-      <c r="AT39" s="10"/>
-      <c r="AU39" s="10"/>
-      <c r="AV39" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW39" s="11"/>
-      <c r="AX39" s="11"/>
-      <c r="AY39" s="11"/>
-      <c r="AZ39" s="11"/>
-      <c r="BA39" s="11"/>
-      <c r="BB39" s="11"/>
-      <c r="BC39" s="11"/>
-      <c r="BD39" s="11"/>
-      <c r="BE39" s="11"/>
-      <c r="BF39" s="11"/>
-      <c r="BG39" s="11"/>
-      <c r="BH39" s="11"/>
-      <c r="BI39" s="12">
-        <v>550</v>
-      </c>
-      <c r="BJ39" s="12"/>
-      <c r="BK39" s="12"/>
-    </row>
-    <row r="41" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
-      <c r="AB41" s="3"/>
-      <c r="AC41" s="3"/>
-      <c r="AD41" s="3"/>
-      <c r="AE41" s="3"/>
-      <c r="AF41" s="3"/>
-      <c r="AG41" s="3"/>
-      <c r="AH41" s="3"/>
-      <c r="AI41" s="3"/>
-      <c r="AJ41" s="3"/>
-      <c r="AK41" s="3"/>
-      <c r="AL41" s="3"/>
-      <c r="AM41" s="3"/>
-      <c r="AN41" s="3"/>
-      <c r="AO41" s="3"/>
-      <c r="AP41" s="3"/>
-      <c r="AQ41" s="3"/>
-      <c r="AR41" s="3"/>
-      <c r="AS41" s="3"/>
-      <c r="AT41" s="3"/>
-      <c r="AU41" s="3"/>
-      <c r="AV41" s="3"/>
-      <c r="AW41" s="3"/>
-      <c r="AX41" s="3"/>
-      <c r="AY41" s="3"/>
-      <c r="AZ41" s="3"/>
-      <c r="BA41" s="3"/>
-      <c r="BB41" s="3"/>
-      <c r="BC41" s="3"/>
-      <c r="BD41" s="3"/>
-      <c r="BE41" s="3"/>
-      <c r="BF41" s="3"/>
-      <c r="BG41" s="3"/>
-      <c r="BH41" s="3"/>
-      <c r="BI41" s="3"/>
-      <c r="BJ41" s="3"/>
-      <c r="BK41" s="3"/>
-      <c r="BL41" s="3"/>
-      <c r="BM41" s="3"/>
-      <c r="BN41" s="3"/>
-      <c r="BO41" s="3"/>
-      <c r="BP41" s="3"/>
-      <c r="BQ41" s="3"/>
-      <c r="BR41" s="3"/>
-      <c r="BS41" s="3"/>
-      <c r="BT41" s="3"/>
-      <c r="BU41" s="3"/>
-      <c r="BV41" s="3"/>
-      <c r="BW41" s="3"/>
-      <c r="BX41" s="3"/>
-      <c r="BY41" s="3"/>
-      <c r="BZ41" s="3"/>
-      <c r="CA41" s="3"/>
-      <c r="CB41" s="3"/>
-      <c r="CC41" s="3"/>
-      <c r="CD41" s="3"/>
-      <c r="CE41" s="3"/>
-      <c r="CF41" s="3"/>
-    </row>
-    <row r="42" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+    <row r="42" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AC42" s="3"/>
-      <c r="AD42" s="3"/>
-      <c r="AE42" s="3"/>
-      <c r="AF42" s="3"/>
-      <c r="AG42" s="3"/>
-      <c r="AH42" s="3"/>
-      <c r="AI42" s="3"/>
-      <c r="AJ42" s="3"/>
-      <c r="AK42" s="3"/>
-      <c r="AL42" s="3"/>
-      <c r="AM42" s="3"/>
-      <c r="AN42" s="3"/>
-      <c r="AO42" s="3"/>
-      <c r="AP42" s="3"/>
-      <c r="AQ42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR42" s="3"/>
-      <c r="AS42" s="3"/>
-      <c r="AT42" s="3"/>
-      <c r="AU42" s="3"/>
-      <c r="AV42" s="3"/>
-      <c r="AW42" s="3"/>
-      <c r="AX42" s="3"/>
-      <c r="AY42" s="3"/>
-      <c r="AZ42" s="3"/>
-      <c r="BA42" s="3"/>
-      <c r="BB42" s="3"/>
-      <c r="BC42" s="3"/>
-      <c r="BD42" s="3"/>
-      <c r="BE42" s="3"/>
-      <c r="BF42" s="3"/>
-      <c r="BG42" s="3"/>
-      <c r="BH42" s="3"/>
-      <c r="BI42" s="3"/>
-      <c r="BJ42" s="3"/>
-      <c r="BK42" s="3"/>
-      <c r="BL42" s="3"/>
-      <c r="BM42" s="3"/>
-      <c r="BN42" s="3"/>
-      <c r="BO42" s="3"/>
-      <c r="BP42" s="3"/>
-      <c r="BQ42" s="3"/>
-      <c r="BR42" s="3"/>
-      <c r="BS42" s="3"/>
-      <c r="BT42" s="3"/>
-      <c r="BU42" s="3"/>
-      <c r="BV42" s="3"/>
-      <c r="BW42" s="3"/>
-      <c r="BX42" s="3"/>
-      <c r="BY42" s="3"/>
-      <c r="BZ42" s="3"/>
-      <c r="CA42" s="3"/>
-      <c r="CB42" s="3"/>
-      <c r="CC42" s="3"/>
-      <c r="CD42" s="3"/>
-      <c r="CE42" s="3"/>
-      <c r="CF42" s="3"/>
-    </row>
-    <row r="43" ht="42" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="5"/>
-      <c r="W43" s="5"/>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="5"/>
-      <c r="AA43" s="5"/>
-      <c r="AB43" s="5"/>
-      <c r="AC43" s="5"/>
-      <c r="AD43" s="5"/>
-      <c r="AE43" s="5"/>
-      <c r="AF43" s="5"/>
-      <c r="AG43" s="5"/>
-      <c r="AH43" s="5"/>
-      <c r="AI43" s="5"/>
-      <c r="AJ43" s="5"/>
-      <c r="AK43" s="5"/>
-      <c r="AL43" s="5"/>
-      <c r="AM43" s="5"/>
-      <c r="AN43" s="5"/>
-      <c r="AO43" s="5"/>
-      <c r="AP43" s="5"/>
-      <c r="AQ43" s="5"/>
-      <c r="AR43" s="5"/>
-      <c r="AS43" s="5"/>
-      <c r="AT43" s="5"/>
-      <c r="AU43" s="5"/>
-      <c r="AV43" s="5"/>
-      <c r="AW43" s="5"/>
-      <c r="AX43" s="5"/>
-      <c r="AY43" s="5"/>
-      <c r="AZ43" s="5"/>
-      <c r="BA43" s="5"/>
-      <c r="BB43" s="5"/>
-      <c r="BC43" s="5"/>
-      <c r="BD43" s="5"/>
-      <c r="BE43" s="5"/>
-      <c r="BF43" s="5"/>
-      <c r="BG43" s="5"/>
-      <c r="BH43" s="5"/>
-      <c r="BI43" s="5"/>
-      <c r="BJ43" s="5"/>
-      <c r="BK43" s="5"/>
-      <c r="BL43" s="5"/>
-      <c r="BM43" s="5"/>
-      <c r="BN43" s="5"/>
-      <c r="BO43" s="5"/>
-      <c r="BP43" s="5"/>
-      <c r="BQ43" s="5"/>
-      <c r="BR43" s="5"/>
-      <c r="BS43" s="5"/>
-      <c r="BT43" s="5"/>
-      <c r="BU43" s="5"/>
-      <c r="BV43" s="5"/>
-      <c r="BW43" s="5"/>
-      <c r="BX43" s="5"/>
-      <c r="BY43" s="5"/>
-      <c r="BZ43" s="5"/>
-      <c r="CA43" s="5"/>
-      <c r="CB43" s="5"/>
-      <c r="CC43" s="5"/>
-      <c r="CD43" s="5"/>
-      <c r="CE43" s="5"/>
-      <c r="CF43" s="5"/>
-    </row>
-    <row r="45" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="2"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="2"/>
-      <c r="X45" s="2"/>
-      <c r="Y45" s="2"/>
-      <c r="Z45" s="2"/>
-      <c r="AA45" s="2"/>
-      <c r="AB45" s="2"/>
-      <c r="AC45" s="2"/>
-      <c r="AD45" s="2"/>
-      <c r="AE45" s="2"/>
-      <c r="AF45" s="2"/>
-      <c r="AG45" s="2"/>
-      <c r="AH45" s="2"/>
-      <c r="AI45" s="2"/>
-      <c r="AJ45" s="2"/>
-      <c r="AK45" s="2"/>
-      <c r="AL45" s="2"/>
-      <c r="AM45" s="2"/>
-      <c r="AN45" s="2"/>
-      <c r="AO45" s="2"/>
-      <c r="AP45" s="2"/>
-      <c r="AQ45" s="2"/>
-      <c r="AR45" s="2"/>
-      <c r="AS45" s="2"/>
-      <c r="AT45" s="2"/>
-      <c r="AU45" s="2"/>
-      <c r="AV45" s="2"/>
-      <c r="AW45" s="2"/>
-      <c r="AX45" s="2"/>
-      <c r="AY45" s="2"/>
-      <c r="AZ45" s="2"/>
-      <c r="BA45" s="2"/>
-      <c r="BB45" s="2"/>
-      <c r="BC45" s="2"/>
-      <c r="BD45" s="2"/>
-      <c r="BE45" s="2"/>
-      <c r="BF45" s="2"/>
-      <c r="BG45" s="2"/>
-      <c r="BH45" s="2"/>
-      <c r="BI45" s="2"/>
-      <c r="BJ45" s="2"/>
-      <c r="BK45" s="2"/>
-      <c r="BL45" s="2"/>
-      <c r="BM45" s="2"/>
-      <c r="BN45" s="2"/>
-      <c r="BO45" s="2"/>
-      <c r="BP45" s="2"/>
-      <c r="BQ45" s="2"/>
-      <c r="BR45" s="2"/>
-      <c r="BS45" s="2"/>
-      <c r="BT45" s="2"/>
-      <c r="BU45" s="2"/>
-      <c r="BV45" s="2"/>
-      <c r="BW45" s="2"/>
-      <c r="BX45" s="2"/>
-      <c r="BY45" s="2"/>
-      <c r="BZ45" s="2"/>
-      <c r="CA45" s="2"/>
-      <c r="CB45" s="2"/>
-      <c r="CC45" s="2"/>
-      <c r="CD45" s="2"/>
-      <c r="CE45" s="2"/>
-      <c r="CF45" s="2"/>
-    </row>
-    <row r="46" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="2"/>
-      <c r="AE46" s="2"/>
-      <c r="AF46" s="2"/>
-      <c r="AG46" s="2"/>
-      <c r="AH46" s="2"/>
-      <c r="AI46" s="2"/>
-      <c r="AJ46" s="2"/>
-      <c r="AK46" s="2"/>
-      <c r="AL46" s="2"/>
-      <c r="AM46" s="2"/>
-      <c r="AN46" s="2"/>
-      <c r="AO46" s="2"/>
-      <c r="AP46" s="2"/>
-      <c r="AQ46" s="2"/>
-      <c r="AR46" s="2"/>
-      <c r="AS46" s="2"/>
-      <c r="AT46" s="2"/>
-      <c r="AU46" s="2"/>
-      <c r="AV46" s="2"/>
-      <c r="AW46" s="2"/>
-      <c r="AX46" s="2"/>
-      <c r="AY46" s="2"/>
-      <c r="AZ46" s="2"/>
-      <c r="BA46" s="2"/>
-      <c r="BB46" s="2"/>
-      <c r="BC46" s="2"/>
-      <c r="BD46" s="2"/>
-      <c r="BE46" s="2"/>
-      <c r="BF46" s="2"/>
-      <c r="BG46" s="2"/>
-      <c r="BH46" s="2"/>
-      <c r="BI46" s="2"/>
-      <c r="BJ46" s="2"/>
-      <c r="BK46" s="2"/>
-      <c r="BL46" s="2"/>
-      <c r="BM46" s="2"/>
-      <c r="BN46" s="2"/>
-      <c r="BO46" s="2"/>
-      <c r="BP46" s="2"/>
-      <c r="BQ46" s="2"/>
-      <c r="BR46" s="2"/>
-      <c r="BS46" s="2"/>
-      <c r="BT46" s="2"/>
-      <c r="BU46" s="2"/>
-      <c r="BV46" s="2"/>
-      <c r="BW46" s="2"/>
-      <c r="BX46" s="2"/>
-      <c r="BY46" s="2"/>
-      <c r="BZ46" s="2"/>
-      <c r="CA46" s="2"/>
-      <c r="CB46" s="2"/>
-      <c r="CC46" s="2"/>
-      <c r="CD46" s="2"/>
-      <c r="CE46" s="2"/>
-      <c r="CF46" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="2"/>
+      <c r="AE42" s="2"/>
+      <c r="AF42" s="2"/>
+      <c r="AG42" s="2"/>
+      <c r="AH42" s="2"/>
+      <c r="AI42" s="2"/>
+      <c r="AJ42" s="2"/>
+      <c r="AK42" s="2"/>
+      <c r="AL42" s="2"/>
+      <c r="AM42" s="2"/>
+      <c r="AN42" s="2"/>
+      <c r="AO42" s="2"/>
+      <c r="AP42" s="2"/>
+      <c r="AQ42" s="2"/>
+      <c r="AR42" s="2"/>
+      <c r="AS42" s="2"/>
+      <c r="AT42" s="2"/>
+      <c r="AU42" s="2"/>
+      <c r="AV42" s="2"/>
+      <c r="AW42" s="2"/>
+      <c r="AX42" s="2"/>
+      <c r="AY42" s="2"/>
+      <c r="AZ42" s="2"/>
+      <c r="BA42" s="2"/>
+      <c r="BB42" s="2"/>
+      <c r="BC42" s="2"/>
+      <c r="BD42" s="2"/>
+      <c r="BE42" s="2"/>
+      <c r="BF42" s="2"/>
+      <c r="BG42" s="2"/>
+      <c r="BH42" s="2"/>
+      <c r="BI42" s="2"/>
+      <c r="BJ42" s="2"/>
+      <c r="BK42" s="2"/>
+      <c r="BL42" s="2"/>
+      <c r="BM42" s="2"/>
+      <c r="BN42" s="2"/>
+      <c r="BO42" s="2"/>
+      <c r="BP42" s="2"/>
+      <c r="BQ42" s="2"/>
+      <c r="BR42" s="2"/>
+      <c r="BS42" s="2"/>
+      <c r="BT42" s="2"/>
+      <c r="BU42" s="2"/>
+      <c r="BV42" s="2"/>
+      <c r="BW42" s="2"/>
+      <c r="BX42" s="2"/>
+      <c r="BY42" s="2"/>
+      <c r="BZ42" s="2"/>
+      <c r="CA42" s="2"/>
+      <c r="CB42" s="2"/>
+      <c r="CC42" s="2"/>
+      <c r="CD42" s="2"/>
+      <c r="CE42" s="2"/>
+      <c r="CF42" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="234">
+  <mergeCells count="227">
     <mergeCell ref="A1:CF1"/>
     <mergeCell ref="A2:CF2"/>
     <mergeCell ref="A3:CF3"/>
@@ -4167,86 +3902,79 @@
     <mergeCell ref="BQ27:BV27"/>
     <mergeCell ref="BW27:CA27"/>
     <mergeCell ref="CB27:CF27"/>
-    <mergeCell ref="A29:CF29"/>
-    <mergeCell ref="A30:Q30"/>
-    <mergeCell ref="R30:AH30"/>
-    <mergeCell ref="AI30:AX30"/>
-    <mergeCell ref="AY30:BO30"/>
-    <mergeCell ref="BP30:CF30"/>
-    <mergeCell ref="A31:Q31"/>
-    <mergeCell ref="R31:AH31"/>
-    <mergeCell ref="AI31:AX31"/>
-    <mergeCell ref="AY31:BO31"/>
-    <mergeCell ref="BP31:CF31"/>
-    <mergeCell ref="A33:U33"/>
-    <mergeCell ref="V33:AP33"/>
-    <mergeCell ref="AQ33:BK33"/>
-    <mergeCell ref="BL33:CF33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="F34:R34"/>
-    <mergeCell ref="S34:U34"/>
-    <mergeCell ref="V34:Z34"/>
-    <mergeCell ref="AA34:AM34"/>
-    <mergeCell ref="AN34:AP34"/>
-    <mergeCell ref="AQ34:AU34"/>
-    <mergeCell ref="AV34:BH34"/>
-    <mergeCell ref="BI34:BK34"/>
-    <mergeCell ref="BL34:BP34"/>
-    <mergeCell ref="BQ34:CC34"/>
-    <mergeCell ref="CD34:CF34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="F35:R35"/>
-    <mergeCell ref="S35:U35"/>
-    <mergeCell ref="V35:Z35"/>
-    <mergeCell ref="AA35:AM35"/>
-    <mergeCell ref="AN35:AP35"/>
-    <mergeCell ref="AQ35:AU35"/>
-    <mergeCell ref="AV35:BH35"/>
-    <mergeCell ref="BI35:BK35"/>
-    <mergeCell ref="BL35:BP35"/>
-    <mergeCell ref="BQ35:CC35"/>
-    <mergeCell ref="CD35:CF35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="F36:R36"/>
-    <mergeCell ref="S36:U36"/>
-    <mergeCell ref="V36:Z36"/>
-    <mergeCell ref="AA36:AM36"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ36:AU36"/>
-    <mergeCell ref="AV36:BH36"/>
-    <mergeCell ref="BI36:BK36"/>
-    <mergeCell ref="BL36:BP36"/>
-    <mergeCell ref="BQ36:CC36"/>
-    <mergeCell ref="CD36:CF36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="F37:R37"/>
-    <mergeCell ref="S37:U37"/>
-    <mergeCell ref="V37:Z37"/>
-    <mergeCell ref="AA37:AM37"/>
-    <mergeCell ref="AN37:AP37"/>
-    <mergeCell ref="AQ37:AU37"/>
-    <mergeCell ref="AV37:BH37"/>
-    <mergeCell ref="BI37:BK37"/>
-    <mergeCell ref="BL37:BP37"/>
-    <mergeCell ref="BQ37:CC37"/>
-    <mergeCell ref="CD37:CF37"/>
-    <mergeCell ref="AQ38:AU38"/>
-    <mergeCell ref="AV38:BH38"/>
-    <mergeCell ref="BI38:BK38"/>
-    <mergeCell ref="AQ39:AU39"/>
-    <mergeCell ref="AV39:BH39"/>
-    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="A29:U29"/>
+    <mergeCell ref="V29:AP29"/>
+    <mergeCell ref="AQ29:BK29"/>
+    <mergeCell ref="BL29:CF29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="G30:P30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:AA30"/>
+    <mergeCell ref="AB30:AK30"/>
+    <mergeCell ref="AL30:AP30"/>
+    <mergeCell ref="AQ30:AV30"/>
+    <mergeCell ref="AW30:BF30"/>
+    <mergeCell ref="BG30:BK30"/>
+    <mergeCell ref="BL30:BQ30"/>
+    <mergeCell ref="BR30:CA30"/>
+    <mergeCell ref="CB30:CF30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="G31:P31"/>
+    <mergeCell ref="Q31:U31"/>
+    <mergeCell ref="V31:AA31"/>
+    <mergeCell ref="AB31:AK31"/>
+    <mergeCell ref="AL31:AP31"/>
+    <mergeCell ref="AQ31:AV31"/>
+    <mergeCell ref="AW31:BF31"/>
+    <mergeCell ref="BG31:BK31"/>
+    <mergeCell ref="BL31:BQ31"/>
+    <mergeCell ref="BR31:CA31"/>
+    <mergeCell ref="CB31:CF31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="G32:P32"/>
+    <mergeCell ref="Q32:U32"/>
+    <mergeCell ref="V32:AA32"/>
+    <mergeCell ref="AB32:AK32"/>
+    <mergeCell ref="AL32:AP32"/>
+    <mergeCell ref="AQ32:AV32"/>
+    <mergeCell ref="AW32:BF32"/>
+    <mergeCell ref="BG32:BK32"/>
+    <mergeCell ref="BL32:BQ32"/>
+    <mergeCell ref="BR32:CA32"/>
+    <mergeCell ref="CB32:CF32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="G33:P33"/>
+    <mergeCell ref="Q33:U33"/>
+    <mergeCell ref="V33:AA33"/>
+    <mergeCell ref="AB33:AK33"/>
+    <mergeCell ref="AL33:AP33"/>
+    <mergeCell ref="AQ33:AV33"/>
+    <mergeCell ref="AW33:BF33"/>
+    <mergeCell ref="BG33:BK33"/>
+    <mergeCell ref="BL33:BQ33"/>
+    <mergeCell ref="BR33:CA33"/>
+    <mergeCell ref="CB33:CF33"/>
+    <mergeCell ref="AQ34:AV34"/>
+    <mergeCell ref="AW34:BF34"/>
+    <mergeCell ref="BG34:BK34"/>
+    <mergeCell ref="AQ35:AV35"/>
+    <mergeCell ref="AW35:BF35"/>
+    <mergeCell ref="BG35:BK35"/>
+    <mergeCell ref="A37:CF37"/>
+    <mergeCell ref="A38:U38"/>
+    <mergeCell ref="V38:AP38"/>
+    <mergeCell ref="AQ38:BK38"/>
+    <mergeCell ref="BL38:CF38"/>
+    <mergeCell ref="A39:U39"/>
+    <mergeCell ref="V39:AP39"/>
+    <mergeCell ref="AQ39:BK39"/>
+    <mergeCell ref="BL39:CF39"/>
     <mergeCell ref="A41:CF41"/>
-    <mergeCell ref="A42:AP42"/>
-    <mergeCell ref="AQ42:CF42"/>
-    <mergeCell ref="A43:AP43"/>
-    <mergeCell ref="AQ43:CF43"/>
-    <mergeCell ref="A45:CF45"/>
-    <mergeCell ref="A46:CF46"/>
+    <mergeCell ref="A42:CF42"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="8" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LGujjar Brother Transport&amp;RPAGE &amp;P / &amp;N</oddFooter>
   </headerFooter>
